--- a/examples/demos/01_build_model_from_brief.xlsx
+++ b/examples/demos/01_build_model_from_brief.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E8A76C-E612-4401-A37F-E61897A8D2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE569F4-4B42-46C8-9727-56EA4314BC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Demo 01 — Build a Monte Carlo model from a brief</t>
   </si>
@@ -54,22 +54,40 @@
     <t>Tools demonstrated: plan_risk_model, propose_distributions_for_inputs, build_model_from_brief, run_simulation, get_simulation_results, restore_deterministic_state</t>
   </si>
   <si>
-    <t>PREREQUISITES</t>
-  </si>
-  <si>
-    <t>Windows Excel with the ModelRisk add-in installed and licensed.</t>
-  </si>
-  <si>
-    <t>modelrisk-mcp connected to Claude (Claude Desktop / Claude Code).</t>
-  </si>
-  <si>
-    <t>PROMPT →  Open C:/Users/timou/source/repos/modelrisk-mcp/examples/demos/01_build_model_from_brief.xlsx in Excel</t>
+    <t>GETTING STARTED</t>
+  </si>
+  <si>
+    <t>You need: Windows Excel with the ModelRisk add-in installed and licensed, and modelrisk-mcp connected to Claude (Claude Desktop or Claude Code).</t>
+  </si>
+  <si>
+    <t>Save the demo gallery folder anywhere on your PC. Once per session, tell Claude where it is and which demo to open:</t>
+  </si>
+  <si>
+    <t>PROMPT →  My ModelRisk demo gallery is in &lt;your folder, e.g. Documents\modelrisk-demos&gt;. Open 01_build_model_from_brief.xlsx from there.</t>
+  </si>
+  <si>
+    <t>Claude remembers the folder for the rest of the session — later demos just need "Open &lt;file&gt; from the demo folder".</t>
+  </si>
+  <si>
+    <t>FAST TRACK — ONE PROMPT DOES IT ALL</t>
+  </si>
+  <si>
+    <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Look at the Model sheet of this workbook. Build a Monte Carlo model: make B6 VosePERT(360,420,500) named Year1Revenue, B7 VosePERT(3%,6%,9%) named Growth, B8 VosePERT(35%,38%,43%) named CogsRatio, wrap B20 as output "NPV", and run 5,000 iterations. Then report the mean and P10/P50/P90 of NPV, the chance NPV is negative, and the P80 NPV.</t>
+  </si>
+  <si>
+    <t>Expected: a fully converted, simulated model + headline risk numbers, in one message.</t>
   </si>
   <si>
     <t>STEP-BY-STEP</t>
   </si>
   <si>
     <t>Open the workbook in Excel.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Open 01_build_model_from_brief.xlsx from the demo folder.</t>
   </si>
   <si>
     <t>Expected: the workbook opens; the Model sheet shows the deterministic 5-year plan with NPV in B20.</t>
@@ -230,7 +248,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +280,46 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
@@ -285,12 +343,37 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E4F92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -335,42 +418,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,7 +765,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -684,233 +773,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="21"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18"/>
+      <c r="B4" s="19"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="18"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="19"/>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="17" t="s">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="18"/>
-    </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="3">
+    </row>
+    <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="19"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" s="14">
         <v>1</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3">
+      <c r="B21" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="14">
         <v>2</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3">
+      <c r="B25" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="14">
         <v>3</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="3">
+      <c r="B29" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="14">
         <v>4</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="3">
+      <c r="B33" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" s="14">
         <v>5</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="3">
+      <c r="B37" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="14">
         <v>6</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" s="18"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B40" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B41" s="4" t="s">
-        <v>30</v>
+      <c r="B41" s="11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="17" t="s">
+      <c r="B42" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="18"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" s="5"/>
-      <c r="B45" s="1" t="s">
+    </row>
+    <row r="43" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="6"/>
-      <c r="B46" s="1" t="s">
+    <row r="45" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="18" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A47" s="7"/>
-      <c r="B47" s="1" t="s">
+      <c r="B45" s="19"/>
+    </row>
+    <row r="46" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" s="2"/>
-      <c r="B48" s="1" t="s">
+    <row r="47" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="11" t="s">
         <v>36</v>
       </c>
     </row>
+    <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="19"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" s="15"/>
+      <c r="B51" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" s="16"/>
+      <c r="B52" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A53" s="17"/>
+      <c r="B53" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" s="12"/>
+      <c r="B54" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A44:B44"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A45:B45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -930,242 +1046,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="A1" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="A4" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="3">
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="9">
+    <row r="6" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="3">
         <v>420</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4">
         <v>0.06</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="10">
+      <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.38</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>46</v>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="9">
+      <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="3">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="10">
+      <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="4">
         <v>0.03</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="10">
+      <c r="A11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="4">
         <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
+      <c r="A13" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>55</v>
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="7">
         <f>B6</f>
         <v>420</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="7">
         <f>B15*(1+$B$7)</f>
         <v>445.20000000000005</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="7">
         <f>C15*(1+$B$7)</f>
         <v>471.91200000000009</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="7">
         <f>D15*(1+$B$7)</f>
         <v>500.22672000000011</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="7">
         <f>E15*(1+$B$7)</f>
         <v>530.24032320000015</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="13">
+      <c r="A16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="7">
         <f>-B15*$B$8</f>
         <v>-159.6</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="7">
         <f>-C15*$B$8</f>
         <v>-169.17600000000002</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="7">
         <f>-D15*$B$8</f>
         <v>-179.32656000000003</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="7">
         <f>-E15*$B$8</f>
         <v>-190.08615360000005</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="7">
         <f>-F15*$B$8</f>
         <v>-201.49132281600006</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="13">
+      <c r="A17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="7">
         <f>-$B$9</f>
         <v>-180</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="7">
         <f>B17*(1+$B$10)</f>
         <v>-185.4</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="7">
         <f>C17*(1+$B$10)</f>
         <v>-190.96200000000002</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="7">
         <f>D17*(1+$B$10)</f>
         <v>-196.69086000000001</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="7">
         <f>E17*(1+$B$10)</f>
         <v>-202.59158580000002</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="15">
+      <c r="A18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="9">
         <f>SUM(B15:B17)</f>
         <v>80.399999999999977</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="9">
         <f>SUM(C15:C17)</f>
         <v>90.623999999999995</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="9">
         <f>SUM(D15:D17)</f>
         <v>101.62344000000004</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="9">
         <f>SUM(E15:E17)</f>
         <v>113.44970640000005</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="9">
         <f>SUM(F15:F17)</f>
         <v>126.15741458400004</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="16">
+      <c r="A20" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="10">
         <f>NPV($B$11,B18:F18)-$B$5</f>
         <v>30.159476205673911</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>61</v>
+      <c r="G20" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/examples/demos/01_build_model_from_brief.xlsx
+++ b/examples/demos/01_build_model_from_brief.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE569F4-4B42-46C8-9727-56EA4314BC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D741DE60-E1F4-4C97-850D-51E215748F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,14 +447,14 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -773,22 +773,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="23"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="19"/>
+      <c r="B4" s="21"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11" t="s">
@@ -806,10 +806,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="19"/>
+      <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="11" t="s">
@@ -832,10 +832,10 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="19"/>
+      <c r="B15" s="21"/>
     </row>
     <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11" t="s">
@@ -853,10 +853,10 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="19"/>
+      <c r="B20" s="21"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="14">
@@ -967,10 +967,10 @@
       </c>
     </row>
     <row r="45" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B45" s="19"/>
+      <c r="B45" s="21"/>
     </row>
     <row r="46" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B46" s="11" t="s">
@@ -988,10 +988,10 @@
       </c>
     </row>
     <row r="50" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="19"/>
+      <c r="B50" s="21"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" s="15"/>
@@ -1049,34 +1049,34 @@
       <c r="A1" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="4" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
@@ -1147,12 +1147,12 @@
       <c r="A13" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="5"/>

--- a/examples/demos/01_build_model_from_brief.xlsx
+++ b/examples/demos/01_build_model_from_brief.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D741DE60-E1F4-4C97-850D-51E215748F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BEAC13-DFED-4A62-B131-6B90B1B2577A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
